--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F560"/>
+  <dimension ref="A1:F564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13858,6 +13858,102 @@
         <v>319.89</v>
       </c>
       <c r="F560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>363.65</v>
+      </c>
+      <c r="C561" t="n">
+        <v>349.04</v>
+      </c>
+      <c r="D561" t="n">
+        <v>329.58</v>
+      </c>
+      <c r="E561" t="n">
+        <v>318.56</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>363.49</v>
+      </c>
+      <c r="C562" t="n">
+        <v>349.07</v>
+      </c>
+      <c r="D562" t="n">
+        <v>329.53</v>
+      </c>
+      <c r="E562" t="n">
+        <v>318.61</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>363.42</v>
+      </c>
+      <c r="C563" t="n">
+        <v>349.11</v>
+      </c>
+      <c r="D563" t="n">
+        <v>329.91</v>
+      </c>
+      <c r="E563" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>363.42</v>
+      </c>
+      <c r="C564" t="n">
+        <v>348.96</v>
+      </c>
+      <c r="D564" t="n">
+        <v>329.63</v>
+      </c>
+      <c r="E564" t="n">
+        <v>318</v>
+      </c>
+      <c r="F564" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13874,7 +13970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B613"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20007,6 +20103,46 @@
       </c>
       <c r="B613" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -20175,28 +20311,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.078088584149185</v>
+        <v>2.991074362111463</v>
       </c>
       <c r="J2" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2184231822061093</v>
+        <v>0.2089094157582375</v>
       </c>
       <c r="M2" t="n">
-        <v>35.5148650271741</v>
+        <v>35.69527984685256</v>
       </c>
       <c r="N2" t="n">
-        <v>2062.101417027604</v>
+        <v>2077.330215895561</v>
       </c>
       <c r="O2" t="n">
-        <v>45.41036684533174</v>
+        <v>45.57773816125106</v>
       </c>
       <c r="P2" t="n">
-        <v>345.8069703749194</v>
+        <v>346.6976064131355</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20253,28 +20389,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2690541205937773</v>
+        <v>0.2609447795623432</v>
       </c>
       <c r="J3" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K3" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09200971106568534</v>
+        <v>0.08776435494959511</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3088684010933</v>
+        <v>5.32361968025613</v>
       </c>
       <c r="N3" t="n">
-        <v>43.18025933858742</v>
+        <v>43.13282982539941</v>
       </c>
       <c r="O3" t="n">
-        <v>6.571168795472189</v>
+        <v>6.567558893942209</v>
       </c>
       <c r="P3" t="n">
-        <v>347.8947603693396</v>
+        <v>347.9777925077943</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20331,28 +20467,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2382367674499692</v>
+        <v>0.2211391856195253</v>
       </c>
       <c r="J4" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K4" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04014671211575471</v>
+        <v>0.03482719967510473</v>
       </c>
       <c r="M4" t="n">
-        <v>7.481138052568483</v>
+        <v>7.523947067071406</v>
       </c>
       <c r="N4" t="n">
-        <v>82.0220958982357</v>
+        <v>82.59234251173579</v>
       </c>
       <c r="O4" t="n">
-        <v>9.056605097840785</v>
+        <v>9.088032928622992</v>
       </c>
       <c r="P4" t="n">
-        <v>336.1166698016341</v>
+        <v>336.2917318117327</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20409,28 +20545,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2439806747973242</v>
+        <v>0.2239008255216655</v>
       </c>
       <c r="J5" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K5" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03272328813343339</v>
+        <v>0.02771191611143231</v>
       </c>
       <c r="M5" t="n">
-        <v>8.50900682348921</v>
+        <v>8.549898146606843</v>
       </c>
       <c r="N5" t="n">
-        <v>106.3562621613543</v>
+        <v>107.191821434041</v>
       </c>
       <c r="O5" t="n">
-        <v>10.31291724786708</v>
+        <v>10.35334831994177</v>
       </c>
       <c r="P5" t="n">
-        <v>327.1286785594753</v>
+        <v>327.3342786574576</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20468,7 +20604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F560"/>
+  <dimension ref="A1:F564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38359,6 +38495,134 @@
         </is>
       </c>
     </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-34.93962067235817,173.57342140172415</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-34.940262473134986,173.57291293746343</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-34.941036245187334,173.57264616923632</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-34.941804930370765,173.57262880211346</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-34.939620109120284,173.5734197887024</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-34.94026253357215,173.5729132576714</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-34.94103625979826,173.57264562199958</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-34.941804878449986,173.5726293460002</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-34.93961986270371,173.57341908300543</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-34.94026261415504,173.5729136846153</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-34.941036148755096,173.57264978099883</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-34.94180431770543,173.5726352199771</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-34.93961986270371,173.57341908300543</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-34.94026231196921,173.57291208357557</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-34.941036230576394,173.57264671647303</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-34.9418055118833,173.57262271058178</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F564"/>
+  <dimension ref="A1:F569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13954,6 +13954,126 @@
         <v>318</v>
       </c>
       <c r="F564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="C565" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="D565" t="n">
+        <v>329.84</v>
+      </c>
+      <c r="E565" t="n">
+        <v>318.29</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="C566" t="n">
+        <v>349.01</v>
+      </c>
+      <c r="D566" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="E566" t="n">
+        <v>318.91</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="C567" t="n">
+        <v>349.33</v>
+      </c>
+      <c r="D567" t="n">
+        <v>331.06</v>
+      </c>
+      <c r="E567" t="n">
+        <v>319.62</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="C568" t="n">
+        <v>349.38</v>
+      </c>
+      <c r="D568" t="n">
+        <v>331.19</v>
+      </c>
+      <c r="E568" t="n">
+        <v>319.79</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="C569" t="n">
+        <v>349.38</v>
+      </c>
+      <c r="D569" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="E569" t="n">
+        <v>320.09</v>
+      </c>
+      <c r="F569" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13970,7 +14090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20143,6 +20263,56 @@
       </c>
       <c r="B617" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -20311,28 +20481,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>2.991074362111463</v>
+        <v>2.886883585928071</v>
       </c>
       <c r="J2" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="K2" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2089094157582375</v>
+        <v>0.19768432797139</v>
       </c>
       <c r="M2" t="n">
-        <v>35.69527984685256</v>
+        <v>35.90653566932644</v>
       </c>
       <c r="N2" t="n">
-        <v>2077.330215895561</v>
+        <v>2094.353064691637</v>
       </c>
       <c r="O2" t="n">
-        <v>45.57773816125106</v>
+        <v>45.76410235863517</v>
       </c>
       <c r="P2" t="n">
-        <v>346.6976064131355</v>
+        <v>347.7671861225497</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20389,28 +20559,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2609447795623432</v>
+        <v>0.2513717133389498</v>
       </c>
       <c r="J3" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="K3" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08776435494959511</v>
+        <v>0.08285240912460246</v>
       </c>
       <c r="M3" t="n">
-        <v>5.32361968025613</v>
+        <v>5.337884890667335</v>
       </c>
       <c r="N3" t="n">
-        <v>43.13282982539941</v>
+        <v>43.0520055868997</v>
       </c>
       <c r="O3" t="n">
-        <v>6.567558893942209</v>
+        <v>6.561402714884959</v>
       </c>
       <c r="P3" t="n">
-        <v>347.9777925077943</v>
+        <v>348.0760899933395</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20467,28 +20637,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2211391856195253</v>
+        <v>0.2024881223846602</v>
       </c>
       <c r="J4" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="K4" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03482719967510473</v>
+        <v>0.02950804196211276</v>
       </c>
       <c r="M4" t="n">
-        <v>7.523947067071406</v>
+        <v>7.562071813268456</v>
       </c>
       <c r="N4" t="n">
-        <v>82.59234251173579</v>
+        <v>82.99981875936261</v>
       </c>
       <c r="O4" t="n">
-        <v>9.088032928622992</v>
+        <v>9.110423632266647</v>
       </c>
       <c r="P4" t="n">
-        <v>336.2917318117327</v>
+        <v>336.4832424303701</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20545,28 +20715,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2239008255216655</v>
+        <v>0.2011043003496899</v>
       </c>
       <c r="J5" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="K5" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02771191611143231</v>
+        <v>0.0225412247704746</v>
       </c>
       <c r="M5" t="n">
-        <v>8.549898146606843</v>
+        <v>8.588805740708755</v>
       </c>
       <c r="N5" t="n">
-        <v>107.191821434041</v>
+        <v>107.9419213395264</v>
       </c>
       <c r="O5" t="n">
-        <v>10.35334831994177</v>
+        <v>10.38951015878643</v>
       </c>
       <c r="P5" t="n">
-        <v>327.3342786574576</v>
+        <v>327.5683568186696</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20604,7 +20774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F564"/>
+  <dimension ref="A1:F569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38623,6 +38793,166 @@
         </is>
       </c>
     </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-34.939619123453966,173.57341696591448</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-34.940261526285965,173.57290792087235</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-34.94103616921043,173.57264901486738</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-34.94180521074293,173.572625865125</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-34.939619123453966,173.57341696591448</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-34.94026241269782,173.57291261725547</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-34.9410360347896,173.5726540494454</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-34.94180456692528,173.57263260932072</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-34.93962127079837,173.57342311555973</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-34.94026305736087,173.57291603280692</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-34.94103581270255,173.57266236744385</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-34.94180382964978,173.57264033251246</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-34.93962127079837,173.57342311555973</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-34.94026315808946,173.57291656648684</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-34.941035774713924,173.57266379025936</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-34.94180365311896,173.57264218172736</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-34.9396213412031,173.57342331718746</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-34.94026315808946,173.57291656648684</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-34.94103568412557,173.5726671831271</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-34.9418033415939,173.57264544504778</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F569"/>
+  <dimension ref="A1:F572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14074,6 +14074,78 @@
         <v>320.09</v>
       </c>
       <c r="F569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>356.97</v>
+      </c>
+      <c r="C570" t="n">
+        <v>348.89</v>
+      </c>
+      <c r="D570" t="n">
+        <v>331.54</v>
+      </c>
+      <c r="E570" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="C571" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="D571" t="n">
+        <v>331.65</v>
+      </c>
+      <c r="E571" t="n">
+        <v>319.89</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>358.76</v>
+      </c>
+      <c r="C572" t="n">
+        <v>348.52</v>
+      </c>
+      <c r="D572" t="n">
+        <v>331.3</v>
+      </c>
+      <c r="E572" t="n">
+        <v>319.83</v>
+      </c>
+      <c r="F572" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14090,7 +14162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B622"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20313,6 +20385,36 @@
       </c>
       <c r="B622" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -20481,28 +20583,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>2.886883585928071</v>
+        <v>2.820809133411617</v>
       </c>
       <c r="J2" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K2" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.19768432797139</v>
+        <v>0.1903595869287634</v>
       </c>
       <c r="M2" t="n">
-        <v>35.90653566932644</v>
+        <v>36.05410264807741</v>
       </c>
       <c r="N2" t="n">
-        <v>2094.353064691637</v>
+        <v>2107.566232897029</v>
       </c>
       <c r="O2" t="n">
-        <v>45.76410235863517</v>
+        <v>45.908237092019</v>
       </c>
       <c r="P2" t="n">
-        <v>347.7671861225497</v>
+        <v>348.4485177827052</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20559,28 +20661,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2513717133389498</v>
+        <v>0.2454514751227602</v>
       </c>
       <c r="J3" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K3" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08285240912460246</v>
+        <v>0.07978398216603722</v>
       </c>
       <c r="M3" t="n">
-        <v>5.337884890667335</v>
+        <v>5.347215679656794</v>
       </c>
       <c r="N3" t="n">
-        <v>43.0520055868997</v>
+        <v>43.02009420866756</v>
       </c>
       <c r="O3" t="n">
-        <v>6.561402714884959</v>
+        <v>6.558970514392297</v>
       </c>
       <c r="P3" t="n">
-        <v>348.0760899933395</v>
+        <v>348.1371538406129</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20637,28 +20739,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2024881223846602</v>
+        <v>0.1923668569299913</v>
       </c>
       <c r="J4" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K4" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02950804196211276</v>
+        <v>0.02681979626522668</v>
       </c>
       <c r="M4" t="n">
-        <v>7.562071813268456</v>
+        <v>7.578394683859329</v>
       </c>
       <c r="N4" t="n">
-        <v>82.99981875936261</v>
+        <v>83.1312430209455</v>
       </c>
       <c r="O4" t="n">
-        <v>9.110423632266647</v>
+        <v>9.1176336305505</v>
       </c>
       <c r="P4" t="n">
-        <v>336.4832424303701</v>
+        <v>336.5876351262783</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20715,28 +20817,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2011043003496899</v>
+        <v>0.1883562300316216</v>
       </c>
       <c r="J5" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K5" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0225412247704746</v>
+        <v>0.01988272373420352</v>
       </c>
       <c r="M5" t="n">
-        <v>8.588805740708755</v>
+        <v>8.606973476623624</v>
       </c>
       <c r="N5" t="n">
-        <v>107.9419213395264</v>
+        <v>108.2749843557175</v>
       </c>
       <c r="O5" t="n">
-        <v>10.38951015878643</v>
+        <v>10.40552662558304</v>
       </c>
       <c r="P5" t="n">
-        <v>327.5683568186696</v>
+        <v>327.6998403663248</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20774,7 +20876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F569"/>
+  <dimension ref="A1:F572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38953,6 +39055,102 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-34.93959715715859,173.57335405808587</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-34.94026217094915,173.57291133642372</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-34.941035672436755,173.57266762091652</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-34.94180367388728,173.57264196417267</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-34.939600888614926,173.5733647443493</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-34.940262191094874,173.57291144315968</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-34.941035640292476,173.57266882483734</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-34.941803549277274,173.57264326950084</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-34.939603458390906,173.57337210375766</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-34.940261425557324,173.57290738719243</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-34.94103574256968,173.57266499418017</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-34.94180361158229,173.57264261683676</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
